--- a/bom/Driver_Inductor_2.1.xlsx
+++ b/bom/Driver_Inductor_2.1.xlsx
@@ -46,9 +46,6 @@
     <t>C5,C6</t>
   </si>
   <si>
-    <t>220p</t>
-  </si>
-  <si>
     <t>C9,C11,C15,C16,C30,C31,C34,C35,C36</t>
   </si>
   <si>
@@ -151,15 +148,9 @@
     <t>LED_SMD:LED_0805_2012Metric_Pad1.15x1.40mm_HandSolder</t>
   </si>
   <si>
-    <t>KP-2012SURCK</t>
-  </si>
-  <si>
     <t>D10</t>
   </si>
   <si>
-    <t>FYLS-0805UBC</t>
-  </si>
-  <si>
     <t>D12</t>
   </si>
   <si>
@@ -344,6 +335,15 @@
   </si>
   <si>
     <t>Current Sensor</t>
+  </si>
+  <si>
+    <t>LTST-C171TBKT</t>
+  </si>
+  <si>
+    <t>EC04-0805QRC/E-AV</t>
+  </si>
+  <si>
+    <t>100p</t>
   </si>
 </sst>
 </file>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -849,7 +849,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -857,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -866,15 +866,15 @@
         <v>2</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -883,32 +883,32 @@
         <v>9</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -917,32 +917,32 @@
         <v>2</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="1">
         <v>8</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
@@ -951,15 +951,15 @@
         <v>1</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
@@ -968,15 +968,15 @@
         <v>1</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -985,69 +985,69 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -1056,410 +1056,410 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3">
         <v>4</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D21" s="3">
         <v>2</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D25" s="4">
         <v>1</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B29" s="6">
         <v>120</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D29" s="6">
         <v>6</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B30" s="6">
         <v>47</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D30" s="6">
         <v>12</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D31" s="6">
         <v>2</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D32" s="6">
         <v>3</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B33" s="6">
         <v>560</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D33" s="6">
         <v>5</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D34" s="6">
         <v>6</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" s="6">
         <v>1</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D36" s="6">
         <v>1</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D37" s="7">
         <v>1</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" s="7">
         <v>1</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D39" s="7">
         <v>1</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
